--- a/Scripts_annehuitema2003/data_output/GS2_25-24_sessions/vjcortesa_G2_Income_dist_251007.xlsx
+++ b/Scripts_annehuitema2003/data_output/GS2_25-24_sessions/vjcortesa_G2_Income_dist_251007.xlsx
@@ -368,7 +368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI121"/>
+  <dimension ref="A1:AN121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -534,15 +534,40 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>personal_cost_used</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>house_cost_used</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>total_measures_spent</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pct_personal_of_total_measures</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pct_house_of_total_measures</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>calculated_costs</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>calculated_spendable</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>calculated_difference_spendable</t>
         </is>
@@ -633,12 +658,21 @@
         </is>
       </c>
       <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
         <v>40000</v>
       </c>
-      <c r="AH2">
+      <c r="AM2">
         <v>5000</v>
       </c>
-      <c r="AI2">
+      <c r="AN2">
         <v>0</v>
       </c>
     </row>
@@ -752,12 +786,27 @@
         <v>4</v>
       </c>
       <c r="AG3">
+        <v>7000</v>
+      </c>
+      <c r="AH3">
+        <v>6000</v>
+      </c>
+      <c r="AI3">
+        <v>13000</v>
+      </c>
+      <c r="AJ3">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="AK3">
+        <v>46.15384615384615</v>
+      </c>
+      <c r="AL3">
         <v>78000</v>
       </c>
-      <c r="AH3">
+      <c r="AM3">
         <v>2000</v>
       </c>
-      <c r="AI3">
+      <c r="AN3">
         <v>0</v>
       </c>
     </row>
@@ -865,12 +914,27 @@
         <v>4</v>
       </c>
       <c r="AG4">
+        <v>9500</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>9500</v>
+      </c>
+      <c r="AJ4">
+        <v>100</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
         <v>74500</v>
       </c>
-      <c r="AH4">
+      <c r="AM4">
         <v>2500</v>
       </c>
-      <c r="AI4">
+      <c r="AN4">
         <v>0</v>
       </c>
     </row>
@@ -978,12 +1042,27 @@
         <v>4</v>
       </c>
       <c r="AG5">
+        <v>10750</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>10750</v>
+      </c>
+      <c r="AJ5">
+        <v>100</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
         <v>75750</v>
       </c>
-      <c r="AH5">
+      <c r="AM5">
         <v>1750</v>
       </c>
-      <c r="AI5">
+      <c r="AN5">
         <v>0</v>
       </c>
     </row>
@@ -1097,12 +1176,27 @@
         <v>4</v>
       </c>
       <c r="AG6">
+        <v>5000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>6000</v>
+      </c>
+      <c r="AJ6">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="AK6">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AL6">
         <v>80000</v>
       </c>
-      <c r="AH6">
+      <c r="AM6">
         <v>-3250</v>
       </c>
-      <c r="AI6">
+      <c r="AN6">
         <v>0</v>
       </c>
     </row>
@@ -1191,12 +1285,21 @@
         </is>
       </c>
       <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
         <v>60000</v>
       </c>
-      <c r="AH7">
+      <c r="AM7">
         <v>30000</v>
       </c>
-      <c r="AI7">
+      <c r="AN7">
         <v>0</v>
       </c>
     </row>
@@ -1310,12 +1413,27 @@
         <v>5</v>
       </c>
       <c r="AG8">
+        <v>5000</v>
+      </c>
+      <c r="AH8">
+        <v>6000</v>
+      </c>
+      <c r="AI8">
+        <v>11000</v>
+      </c>
+      <c r="AJ8">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="AK8">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="AL8">
         <v>133000</v>
       </c>
-      <c r="AH8">
+      <c r="AM8">
         <v>7000</v>
       </c>
-      <c r="AI8">
+      <c r="AN8">
         <v>0</v>
       </c>
     </row>
@@ -1429,12 +1547,27 @@
         <v>5</v>
       </c>
       <c r="AG9">
+        <v>15000</v>
+      </c>
+      <c r="AH9">
+        <v>8000</v>
+      </c>
+      <c r="AI9">
+        <v>23000</v>
+      </c>
+      <c r="AJ9">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="AK9">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="AL9">
         <v>115000</v>
       </c>
-      <c r="AH9">
+      <c r="AM9">
         <v>2000</v>
       </c>
-      <c r="AI9">
+      <c r="AN9">
         <v>0</v>
       </c>
     </row>
@@ -1548,12 +1681,27 @@
         <v>5</v>
       </c>
       <c r="AG10">
+        <v>10000</v>
+      </c>
+      <c r="AH10">
+        <v>9000</v>
+      </c>
+      <c r="AI10">
+        <v>19000</v>
+      </c>
+      <c r="AJ10">
+        <v>52.63157894736842</v>
+      </c>
+      <c r="AK10">
+        <v>47.36842105263158</v>
+      </c>
+      <c r="AL10">
         <v>111000</v>
       </c>
-      <c r="AH10">
+      <c r="AM10">
         <v>1000</v>
       </c>
-      <c r="AI10">
+      <c r="AN10">
         <v>0</v>
       </c>
     </row>
@@ -1661,12 +1809,27 @@
         <v>5</v>
       </c>
       <c r="AG11">
+        <v>14000</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>14000</v>
+      </c>
+      <c r="AJ11">
+        <v>100</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
         <v>111000</v>
       </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
         <v>0</v>
       </c>
     </row>
@@ -1755,12 +1918,21 @@
         </is>
       </c>
       <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
         <v>30000</v>
       </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
         <v>0</v>
       </c>
     </row>
@@ -1868,12 +2040,27 @@
         <v>4</v>
       </c>
       <c r="AG13">
+        <v>1400</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>2400</v>
+      </c>
+      <c r="AJ13">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="AK13">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="AL13">
         <v>67400</v>
       </c>
-      <c r="AH13">
+      <c r="AM13">
         <v>-7400</v>
       </c>
-      <c r="AI13">
+      <c r="AN13">
         <v>0</v>
       </c>
     </row>
@@ -1978,12 +2165,21 @@
         <v>1</v>
       </c>
       <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
         <v>57000</v>
       </c>
-      <c r="AH14">
+      <c r="AM14">
         <v>-4400</v>
       </c>
-      <c r="AI14">
+      <c r="AN14">
         <v>0</v>
       </c>
     </row>
@@ -2088,12 +2284,21 @@
         <v>2</v>
       </c>
       <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
         <v>61000</v>
       </c>
-      <c r="AH15">
+      <c r="AM15">
         <v>-5400</v>
       </c>
-      <c r="AI15">
+      <c r="AN15">
         <v>0</v>
       </c>
     </row>
@@ -2207,12 +2412,27 @@
         <v>4</v>
       </c>
       <c r="AG16">
+        <v>6500</v>
+      </c>
+      <c r="AH16">
+        <v>10000</v>
+      </c>
+      <c r="AI16">
+        <v>16500</v>
+      </c>
+      <c r="AJ16">
+        <v>39.39393939393939</v>
+      </c>
+      <c r="AK16">
+        <v>60.60606060606061</v>
+      </c>
+      <c r="AL16">
         <v>77500</v>
       </c>
-      <c r="AH16">
+      <c r="AM16">
         <v>28100</v>
       </c>
-      <c r="AI16">
+      <c r="AN16">
         <v>0</v>
       </c>
     </row>
@@ -2301,12 +2521,21 @@
         </is>
       </c>
       <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
         <v>50000</v>
       </c>
-      <c r="AH17">
+      <c r="AM17">
         <v>15000</v>
       </c>
-      <c r="AI17">
+      <c r="AN17">
         <v>0</v>
       </c>
     </row>
@@ -2420,12 +2649,27 @@
         <v>3</v>
       </c>
       <c r="AG18">
+        <v>6000</v>
+      </c>
+      <c r="AH18">
+        <v>14000</v>
+      </c>
+      <c r="AI18">
+        <v>20000</v>
+      </c>
+      <c r="AJ18">
+        <v>30</v>
+      </c>
+      <c r="AK18">
+        <v>70</v>
+      </c>
+      <c r="AL18">
         <v>98000</v>
       </c>
-      <c r="AH18">
+      <c r="AM18">
         <v>7000</v>
       </c>
-      <c r="AI18">
+      <c r="AN18">
         <v>0</v>
       </c>
     </row>
@@ -2533,12 +2777,27 @@
         <v>4</v>
       </c>
       <c r="AG19">
+        <v>8500</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>8500</v>
+      </c>
+      <c r="AJ19">
+        <v>100</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
         <v>86500</v>
       </c>
-      <c r="AH19">
+      <c r="AM19">
         <v>10500</v>
       </c>
-      <c r="AI19">
+      <c r="AN19">
         <v>0</v>
       </c>
     </row>
@@ -2646,12 +2905,27 @@
         <v>5</v>
       </c>
       <c r="AG20">
+        <v>6000</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>6000</v>
+      </c>
+      <c r="AJ20">
+        <v>100</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
         <v>84000</v>
       </c>
-      <c r="AH20">
+      <c r="AM20">
         <v>16500</v>
       </c>
-      <c r="AI20">
+      <c r="AN20">
         <v>0</v>
       </c>
     </row>
@@ -2759,12 +3033,27 @@
         <v>5</v>
       </c>
       <c r="AG21">
+        <v>6100</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>6100</v>
+      </c>
+      <c r="AJ21">
+        <v>100</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
         <v>88100</v>
       </c>
-      <c r="AH21">
+      <c r="AM21">
         <v>18400</v>
       </c>
-      <c r="AI21">
+      <c r="AN21">
         <v>0</v>
       </c>
     </row>
@@ -2853,12 +3142,21 @@
         </is>
       </c>
       <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
         <v>75000</v>
       </c>
-      <c r="AH22">
+      <c r="AM22">
         <v>50000</v>
       </c>
-      <c r="AI22">
+      <c r="AN22">
         <v>0</v>
       </c>
     </row>
@@ -2972,12 +3270,27 @@
         <v>2</v>
       </c>
       <c r="AG23">
+        <v>8750</v>
+      </c>
+      <c r="AH23">
+        <v>22000</v>
+      </c>
+      <c r="AI23">
+        <v>30750</v>
+      </c>
+      <c r="AJ23">
+        <v>28.45528455284553</v>
+      </c>
+      <c r="AK23">
+        <v>71.54471544715447</v>
+      </c>
+      <c r="AL23">
         <v>142250</v>
       </c>
-      <c r="AH23">
+      <c r="AM23">
         <v>37750</v>
       </c>
-      <c r="AI23">
+      <c r="AN23">
         <v>0</v>
       </c>
     </row>
@@ -3091,12 +3404,27 @@
         <v>2</v>
       </c>
       <c r="AG24">
+        <v>15250</v>
+      </c>
+      <c r="AH24">
+        <v>10000</v>
+      </c>
+      <c r="AI24">
+        <v>25250</v>
+      </c>
+      <c r="AJ24">
+        <v>60.3960396039604</v>
+      </c>
+      <c r="AK24">
+        <v>39.6039603960396</v>
+      </c>
+      <c r="AL24">
         <v>132750</v>
       </c>
-      <c r="AH24">
+      <c r="AM24">
         <v>35000</v>
       </c>
-      <c r="AI24">
+      <c r="AN24">
         <v>0</v>
       </c>
     </row>
@@ -3204,12 +3532,27 @@
         <v>2</v>
       </c>
       <c r="AG25">
+        <v>18375</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>18375</v>
+      </c>
+      <c r="AJ25">
+        <v>100</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
         <v>125875</v>
       </c>
-      <c r="AH25">
+      <c r="AM25">
         <v>39125</v>
       </c>
-      <c r="AI25">
+      <c r="AN25">
         <v>0</v>
       </c>
     </row>
@@ -3317,12 +3660,27 @@
         <v>2</v>
       </c>
       <c r="AG26">
+        <v>18375</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>18375</v>
+      </c>
+      <c r="AJ26">
+        <v>100</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
         <v>125875</v>
       </c>
-      <c r="AH26">
+      <c r="AM26">
         <v>43250</v>
       </c>
-      <c r="AI26">
+      <c r="AN26">
         <v>0</v>
       </c>
     </row>
@@ -3411,12 +3769,21 @@
         </is>
       </c>
       <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
         <v>115000</v>
       </c>
-      <c r="AH27">
+      <c r="AM27">
         <v>80000</v>
       </c>
-      <c r="AI27">
+      <c r="AN27">
         <v>0</v>
       </c>
     </row>
@@ -3524,12 +3891,27 @@
         <v>4</v>
       </c>
       <c r="AG28">
+        <v>24500</v>
+      </c>
+      <c r="AH28">
+        <v>10000</v>
+      </c>
+      <c r="AI28">
+        <v>34500</v>
+      </c>
+      <c r="AJ28">
+        <v>71.01449275362319</v>
+      </c>
+      <c r="AK28">
+        <v>28.98550724637681</v>
+      </c>
+      <c r="AL28">
         <v>184500</v>
       </c>
-      <c r="AH28">
+      <c r="AM28">
         <v>85500</v>
       </c>
-      <c r="AI28">
+      <c r="AN28">
         <v>0</v>
       </c>
     </row>
@@ -3637,12 +4019,27 @@
         <v>4</v>
       </c>
       <c r="AG29">
+        <v>24500</v>
+      </c>
+      <c r="AH29">
+        <v>22000</v>
+      </c>
+      <c r="AI29">
+        <v>46500</v>
+      </c>
+      <c r="AJ29">
+        <v>52.68817204301075</v>
+      </c>
+      <c r="AK29">
+        <v>47.31182795698925</v>
+      </c>
+      <c r="AL29">
         <v>196500</v>
       </c>
-      <c r="AH29">
+      <c r="AM29">
         <v>79000</v>
       </c>
-      <c r="AI29">
+      <c r="AN29">
         <v>0</v>
       </c>
     </row>
@@ -3750,12 +4147,27 @@
         <v>4</v>
       </c>
       <c r="AG30">
+        <v>24500</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>24500</v>
+      </c>
+      <c r="AJ30">
+        <v>100</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
         <v>174500</v>
       </c>
-      <c r="AH30">
+      <c r="AM30">
         <v>94500</v>
       </c>
-      <c r="AI30">
+      <c r="AN30">
         <v>0</v>
       </c>
     </row>
@@ -3869,12 +4281,27 @@
         <v>5</v>
       </c>
       <c r="AG31">
+        <v>31875</v>
+      </c>
+      <c r="AH31">
+        <v>14000</v>
+      </c>
+      <c r="AI31">
+        <v>45875</v>
+      </c>
+      <c r="AJ31">
+        <v>69.48228882833789</v>
+      </c>
+      <c r="AK31">
+        <v>30.51771117166212</v>
+      </c>
+      <c r="AL31">
         <v>335875</v>
       </c>
-      <c r="AH31">
+      <c r="AM31">
         <v>8625</v>
       </c>
-      <c r="AI31">
+      <c r="AN31">
         <v>0</v>
       </c>
     </row>
@@ -3963,12 +4390,21 @@
         </is>
       </c>
       <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
         <v>40000</v>
       </c>
-      <c r="AH32">
+      <c r="AM32">
         <v>5000</v>
       </c>
-      <c r="AI32">
+      <c r="AN32">
         <v>0</v>
       </c>
     </row>
@@ -4082,12 +4518,27 @@
         <v>3</v>
       </c>
       <c r="AG33">
+        <v>1600</v>
+      </c>
+      <c r="AH33">
+        <v>8000</v>
+      </c>
+      <c r="AI33">
+        <v>9600</v>
+      </c>
+      <c r="AJ33">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AK33">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="AL33">
         <v>72600</v>
       </c>
-      <c r="AH33">
+      <c r="AM33">
         <v>7400</v>
       </c>
-      <c r="AI33">
+      <c r="AN33">
         <v>0</v>
       </c>
     </row>
@@ -4201,12 +4652,27 @@
         <v>4</v>
       </c>
       <c r="AG34">
+        <v>1600</v>
+      </c>
+      <c r="AH34">
+        <v>14000</v>
+      </c>
+      <c r="AI34">
+        <v>15600</v>
+      </c>
+      <c r="AJ34">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="AK34">
+        <v>89.74358974358975</v>
+      </c>
+      <c r="AL34">
         <v>82600</v>
       </c>
-      <c r="AH34">
+      <c r="AM34">
         <v>-200</v>
       </c>
-      <c r="AI34">
+      <c r="AN34">
         <v>0</v>
       </c>
     </row>
@@ -4320,12 +4786,27 @@
         <v>3</v>
       </c>
       <c r="AG35">
+        <v>1600</v>
+      </c>
+      <c r="AH35">
+        <v>10000</v>
+      </c>
+      <c r="AI35">
+        <v>11600</v>
+      </c>
+      <c r="AJ35">
+        <v>13.79310344827586</v>
+      </c>
+      <c r="AK35">
+        <v>86.20689655172413</v>
+      </c>
+      <c r="AL35">
         <v>74600</v>
       </c>
-      <c r="AH35">
+      <c r="AM35">
         <v>200</v>
       </c>
-      <c r="AI35">
+      <c r="AN35">
         <v>0</v>
       </c>
     </row>
@@ -4439,12 +4920,27 @@
         <v>3</v>
       </c>
       <c r="AG36">
+        <v>6000</v>
+      </c>
+      <c r="AH36">
+        <v>1000</v>
+      </c>
+      <c r="AI36">
+        <v>7000</v>
+      </c>
+      <c r="AJ36">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="AK36">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AL36">
         <v>75000</v>
       </c>
-      <c r="AH36">
+      <c r="AM36">
         <v>200</v>
       </c>
-      <c r="AI36">
+      <c r="AN36">
         <v>0</v>
       </c>
     </row>
@@ -4533,12 +5029,21 @@
         </is>
       </c>
       <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
         <v>60000</v>
       </c>
-      <c r="AH37">
+      <c r="AM37">
         <v>30000</v>
       </c>
-      <c r="AI37">
+      <c r="AN37">
         <v>0</v>
       </c>
     </row>
@@ -4646,12 +5151,27 @@
         <v>2</v>
       </c>
       <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>7000</v>
+      </c>
+      <c r="AI38">
+        <v>7000</v>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>100</v>
+      </c>
+      <c r="AL38">
         <v>134000</v>
       </c>
-      <c r="AH38">
+      <c r="AM38">
         <v>6000</v>
       </c>
-      <c r="AI38">
+      <c r="AN38">
         <v>0</v>
       </c>
     </row>
@@ -4759,12 +5279,27 @@
         <v>2</v>
       </c>
       <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>8000</v>
+      </c>
+      <c r="AI39">
+        <v>8000</v>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>100</v>
+      </c>
+      <c r="AL39">
         <v>109000</v>
       </c>
-      <c r="AH39">
+      <c r="AM39">
         <v>7000</v>
       </c>
-      <c r="AI39">
+      <c r="AN39">
         <v>0</v>
       </c>
     </row>
@@ -4872,12 +5407,27 @@
         <v>1</v>
       </c>
       <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>18000</v>
+      </c>
+      <c r="AI40">
+        <v>18000</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>100</v>
+      </c>
+      <c r="AL40">
         <v>115000</v>
       </c>
-      <c r="AH40">
+      <c r="AM40">
         <v>2000</v>
       </c>
-      <c r="AI40">
+      <c r="AN40">
         <v>0</v>
       </c>
     </row>
@@ -4985,12 +5535,27 @@
         <v>1</v>
       </c>
       <c r="AG41">
+        <v>15000</v>
+      </c>
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
+        <v>15000</v>
+      </c>
+      <c r="AJ41">
+        <v>100</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
         <v>112000</v>
       </c>
-      <c r="AH41">
-        <v>0</v>
-      </c>
-      <c r="AI41">
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
         <v>0</v>
       </c>
     </row>
@@ -5079,12 +5644,21 @@
         </is>
       </c>
       <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42">
+        <v>0</v>
+      </c>
+      <c r="AI42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
         <v>30000</v>
       </c>
-      <c r="AH42">
-        <v>0</v>
-      </c>
-      <c r="AI42">
+      <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
         <v>0</v>
       </c>
     </row>
@@ -5192,12 +5766,27 @@
         <v>1</v>
       </c>
       <c r="AG43">
+        <v>1750</v>
+      </c>
+      <c r="AH43">
+        <v>0</v>
+      </c>
+      <c r="AI43">
+        <v>1750</v>
+      </c>
+      <c r="AJ43">
+        <v>100</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
         <v>58750</v>
       </c>
-      <c r="AH43">
+      <c r="AM43">
         <v>1250</v>
       </c>
-      <c r="AI43">
+      <c r="AN43">
         <v>0</v>
       </c>
     </row>
@@ -5305,12 +5894,27 @@
         <v>1</v>
       </c>
       <c r="AG44">
+        <v>3500</v>
+      </c>
+      <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AI44">
+        <v>3500</v>
+      </c>
+      <c r="AJ44">
+        <v>100</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
         <v>76500</v>
       </c>
-      <c r="AH44">
+      <c r="AM44">
         <v>-15250</v>
       </c>
-      <c r="AI44">
+      <c r="AN44">
         <v>0</v>
       </c>
     </row>
@@ -5415,12 +6019,21 @@
         <v>1</v>
       </c>
       <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
         <v>61000</v>
       </c>
-      <c r="AH45">
+      <c r="AM45">
         <v>-16250</v>
       </c>
-      <c r="AI45">
+      <c r="AN45">
         <v>0</v>
       </c>
     </row>
@@ -5525,12 +6138,21 @@
         <v>1</v>
       </c>
       <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
         <v>61000</v>
       </c>
-      <c r="AH46">
+      <c r="AM46">
         <v>-17250</v>
       </c>
-      <c r="AI46">
+      <c r="AN46">
         <v>0</v>
       </c>
     </row>
@@ -5619,12 +6241,21 @@
         </is>
       </c>
       <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47">
+        <v>0</v>
+      </c>
+      <c r="AI47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
         <v>50000</v>
       </c>
-      <c r="AH47">
+      <c r="AM47">
         <v>15000</v>
       </c>
-      <c r="AI47">
+      <c r="AN47">
         <v>0</v>
       </c>
     </row>
@@ -5729,12 +6360,21 @@
         <v>4</v>
       </c>
       <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48">
+        <v>0</v>
+      </c>
+      <c r="AI48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
         <v>108000</v>
       </c>
-      <c r="AH48">
+      <c r="AM48">
         <v>-3000</v>
       </c>
-      <c r="AI48">
+      <c r="AN48">
         <v>0</v>
       </c>
     </row>
@@ -5842,12 +6482,27 @@
         <v>4</v>
       </c>
       <c r="AG49">
+        <v>7700</v>
+      </c>
+      <c r="AH49">
+        <v>0</v>
+      </c>
+      <c r="AI49">
+        <v>7700</v>
+      </c>
+      <c r="AJ49">
+        <v>100</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
         <v>89700</v>
       </c>
-      <c r="AH49">
+      <c r="AM49">
         <v>-2700</v>
       </c>
-      <c r="AI49">
+      <c r="AN49">
         <v>0</v>
       </c>
     </row>
@@ -5952,12 +6607,21 @@
         <v>3</v>
       </c>
       <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50">
+        <v>0</v>
+      </c>
+      <c r="AI50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
         <v>82000</v>
       </c>
-      <c r="AH50">
+      <c r="AM50">
         <v>5300</v>
       </c>
-      <c r="AI50">
+      <c r="AN50">
         <v>0</v>
       </c>
     </row>
@@ -6071,12 +6735,27 @@
         <v>4</v>
       </c>
       <c r="AG51">
+        <v>14000</v>
+      </c>
+      <c r="AH51">
+        <v>32000</v>
+      </c>
+      <c r="AI51">
+        <v>46000</v>
+      </c>
+      <c r="AJ51">
+        <v>30.43478260869566</v>
+      </c>
+      <c r="AK51">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="AL51">
         <v>126000</v>
       </c>
-      <c r="AH51">
+      <c r="AM51">
         <v>38300</v>
       </c>
-      <c r="AI51">
+      <c r="AN51">
         <v>0</v>
       </c>
     </row>
@@ -6165,12 +6844,21 @@
         </is>
       </c>
       <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52">
+        <v>0</v>
+      </c>
+      <c r="AI52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
         <v>75000</v>
       </c>
-      <c r="AH52">
+      <c r="AM52">
         <v>50000</v>
       </c>
-      <c r="AI52">
+      <c r="AN52">
         <v>0</v>
       </c>
     </row>
@@ -6284,12 +6972,27 @@
         <v>4</v>
       </c>
       <c r="AG53">
+        <v>14000</v>
+      </c>
+      <c r="AH53">
+        <v>9000</v>
+      </c>
+      <c r="AI53">
+        <v>23000</v>
+      </c>
+      <c r="AJ53">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="AK53">
+        <v>39.1304347826087</v>
+      </c>
+      <c r="AL53">
         <v>138000</v>
       </c>
-      <c r="AH53">
+      <c r="AM53">
         <v>42000</v>
       </c>
-      <c r="AI53">
+      <c r="AN53">
         <v>0</v>
       </c>
     </row>
@@ -6403,12 +7106,27 @@
         <v>4</v>
       </c>
       <c r="AG54">
+        <v>14000</v>
+      </c>
+      <c r="AH54">
+        <v>24000</v>
+      </c>
+      <c r="AI54">
+        <v>38000</v>
+      </c>
+      <c r="AJ54">
+        <v>36.84210526315789</v>
+      </c>
+      <c r="AK54">
+        <v>63.1578947368421</v>
+      </c>
+      <c r="AL54">
         <v>153000</v>
       </c>
-      <c r="AH54">
+      <c r="AM54">
         <v>19000</v>
       </c>
-      <c r="AI54">
+      <c r="AN54">
         <v>0</v>
       </c>
     </row>
@@ -6516,12 +7234,27 @@
         <v>5</v>
       </c>
       <c r="AG55">
+        <v>25500</v>
+      </c>
+      <c r="AH55">
+        <v>0</v>
+      </c>
+      <c r="AI55">
+        <v>25500</v>
+      </c>
+      <c r="AJ55">
+        <v>100</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
         <v>140500</v>
       </c>
-      <c r="AH55">
+      <c r="AM55">
         <v>8500</v>
       </c>
-      <c r="AI55">
+      <c r="AN55">
         <v>0</v>
       </c>
     </row>
@@ -6629,12 +7362,27 @@
         <v>5</v>
       </c>
       <c r="AG56">
+        <v>19000</v>
+      </c>
+      <c r="AH56">
+        <v>0</v>
+      </c>
+      <c r="AI56">
+        <v>19000</v>
+      </c>
+      <c r="AJ56">
+        <v>100</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
         <v>134000</v>
       </c>
-      <c r="AH56">
+      <c r="AM56">
         <v>4500</v>
       </c>
-      <c r="AI56">
+      <c r="AN56">
         <v>0</v>
       </c>
     </row>
@@ -6723,12 +7471,21 @@
         </is>
       </c>
       <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57">
+        <v>0</v>
+      </c>
+      <c r="AI57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
         <v>115000</v>
       </c>
-      <c r="AH57">
+      <c r="AM57">
         <v>80000</v>
       </c>
-      <c r="AI57">
+      <c r="AN57">
         <v>0</v>
       </c>
     </row>
@@ -6842,12 +7599,27 @@
         <v>4</v>
       </c>
       <c r="AG58">
+        <v>30500</v>
+      </c>
+      <c r="AH58">
+        <v>14000</v>
+      </c>
+      <c r="AI58">
+        <v>44500</v>
+      </c>
+      <c r="AJ58">
+        <v>68.53932584269663</v>
+      </c>
+      <c r="AK58">
+        <v>31.46067415730337</v>
+      </c>
+      <c r="AL58">
         <v>204500</v>
       </c>
-      <c r="AH58">
+      <c r="AM58">
         <v>65500</v>
       </c>
-      <c r="AI58">
+      <c r="AN58">
         <v>0</v>
       </c>
     </row>
@@ -6955,12 +7727,27 @@
         <v>3</v>
       </c>
       <c r="AG59">
+        <v>15500</v>
+      </c>
+      <c r="AH59">
+        <v>0</v>
+      </c>
+      <c r="AI59">
+        <v>15500</v>
+      </c>
+      <c r="AJ59">
+        <v>100</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
         <v>179500</v>
       </c>
-      <c r="AH59">
+      <c r="AM59">
         <v>76000</v>
       </c>
-      <c r="AI59">
+      <c r="AN59">
         <v>0</v>
       </c>
     </row>
@@ -7074,12 +7861,27 @@
         <v>2</v>
       </c>
       <c r="AG60">
+        <v>30500</v>
+      </c>
+      <c r="AH60">
+        <v>19000</v>
+      </c>
+      <c r="AI60">
+        <v>49500</v>
+      </c>
+      <c r="AJ60">
+        <v>61.61616161616161</v>
+      </c>
+      <c r="AK60">
+        <v>38.38383838383838</v>
+      </c>
+      <c r="AL60">
         <v>209500</v>
       </c>
-      <c r="AH60">
+      <c r="AM60">
         <v>56500</v>
       </c>
-      <c r="AI60">
+      <c r="AN60">
         <v>0</v>
       </c>
     </row>
@@ -7187,12 +7989,27 @@
         <v>2</v>
       </c>
       <c r="AG61">
+        <v>38000</v>
+      </c>
+      <c r="AH61">
+        <v>0</v>
+      </c>
+      <c r="AI61">
+        <v>38000</v>
+      </c>
+      <c r="AJ61">
+        <v>100</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
         <v>203000</v>
       </c>
-      <c r="AH61">
+      <c r="AM61">
         <v>43500</v>
       </c>
-      <c r="AI61">
+      <c r="AN61">
         <v>0</v>
       </c>
     </row>
@@ -7281,12 +8098,21 @@
         </is>
       </c>
       <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62">
+        <v>0</v>
+      </c>
+      <c r="AI62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
         <v>40000</v>
       </c>
-      <c r="AH62">
+      <c r="AM62">
         <v>5000</v>
       </c>
-      <c r="AI62">
+      <c r="AN62">
         <v>0</v>
       </c>
     </row>
@@ -7394,12 +8220,27 @@
         <v>4</v>
       </c>
       <c r="AG63">
+        <v>5000</v>
+      </c>
+      <c r="AH63">
+        <v>0</v>
+      </c>
+      <c r="AI63">
+        <v>5000</v>
+      </c>
+      <c r="AJ63">
+        <v>100</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
         <v>70000</v>
       </c>
-      <c r="AH63">
+      <c r="AM63">
         <v>10000</v>
       </c>
-      <c r="AI63">
+      <c r="AN63">
         <v>0</v>
       </c>
     </row>
@@ -7507,12 +8348,27 @@
         <v>4</v>
       </c>
       <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64">
+        <v>9000</v>
+      </c>
+      <c r="AI64">
+        <v>9000</v>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>100</v>
+      </c>
+      <c r="AL64">
         <v>74000</v>
       </c>
-      <c r="AH64">
+      <c r="AM64">
         <v>11000</v>
       </c>
-      <c r="AI64">
+      <c r="AN64">
         <v>0</v>
       </c>
     </row>
@@ -7620,12 +8476,27 @@
         <v>4</v>
       </c>
       <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65">
+        <v>18000</v>
+      </c>
+      <c r="AI65">
+        <v>18000</v>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>100</v>
+      </c>
+      <c r="AL65">
         <v>83000</v>
       </c>
-      <c r="AH65">
+      <c r="AM65">
         <v>3000</v>
       </c>
-      <c r="AI65">
+      <c r="AN65">
         <v>0</v>
       </c>
     </row>
@@ -7733,12 +8604,27 @@
         <v>4</v>
       </c>
       <c r="AG66">
+        <v>7500</v>
+      </c>
+      <c r="AH66">
+        <v>0</v>
+      </c>
+      <c r="AI66">
+        <v>7500</v>
+      </c>
+      <c r="AJ66">
+        <v>100</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
         <v>77500</v>
       </c>
-      <c r="AH66">
+      <c r="AM66">
         <v>500</v>
       </c>
-      <c r="AI66">
+      <c r="AN66">
         <v>0</v>
       </c>
     </row>
@@ -7827,12 +8713,21 @@
         </is>
       </c>
       <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67">
+        <v>0</v>
+      </c>
+      <c r="AI67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
         <v>60000</v>
       </c>
-      <c r="AH67">
+      <c r="AM67">
         <v>30000</v>
       </c>
-      <c r="AI67">
+      <c r="AN67">
         <v>0</v>
       </c>
     </row>
@@ -7946,12 +8841,27 @@
         <v>2</v>
       </c>
       <c r="AG68">
+        <v>9375</v>
+      </c>
+      <c r="AH68">
+        <v>22000</v>
+      </c>
+      <c r="AI68">
+        <v>31375</v>
+      </c>
+      <c r="AJ68">
+        <v>29.8804780876494</v>
+      </c>
+      <c r="AK68">
+        <v>70.11952191235061</v>
+      </c>
+      <c r="AL68">
         <v>123875</v>
       </c>
-      <c r="AH68">
+      <c r="AM68">
         <v>16125</v>
       </c>
-      <c r="AI68">
+      <c r="AN68">
         <v>0</v>
       </c>
     </row>
@@ -8065,12 +8975,27 @@
         <v>2</v>
       </c>
       <c r="AG69">
+        <v>8750</v>
+      </c>
+      <c r="AH69">
+        <v>11000</v>
+      </c>
+      <c r="AI69">
+        <v>19750</v>
+      </c>
+      <c r="AJ69">
+        <v>44.30379746835442</v>
+      </c>
+      <c r="AK69">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="AL69">
         <v>112250</v>
       </c>
-      <c r="AH69">
+      <c r="AM69">
         <v>13875</v>
       </c>
-      <c r="AI69">
+      <c r="AN69">
         <v>0</v>
       </c>
     </row>
@@ -8178,12 +9103,27 @@
         <v>1</v>
       </c>
       <c r="AG70">
+        <v>17375</v>
+      </c>
+      <c r="AH70">
+        <v>0</v>
+      </c>
+      <c r="AI70">
+        <v>17375</v>
+      </c>
+      <c r="AJ70">
+        <v>100</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
         <v>109875</v>
       </c>
-      <c r="AH70">
+      <c r="AM70">
         <v>14000</v>
       </c>
-      <c r="AI70">
+      <c r="AN70">
         <v>0</v>
       </c>
     </row>
@@ -8291,12 +9231,27 @@
         <v>2</v>
       </c>
       <c r="AG71">
+        <v>17375</v>
+      </c>
+      <c r="AH71">
+        <v>0</v>
+      </c>
+      <c r="AI71">
+        <v>17375</v>
+      </c>
+      <c r="AJ71">
+        <v>100</v>
+      </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
         <v>109875</v>
       </c>
-      <c r="AH71">
+      <c r="AM71">
         <v>14125</v>
       </c>
-      <c r="AI71">
+      <c r="AN71">
         <v>0</v>
       </c>
     </row>
@@ -8385,12 +9340,21 @@
         </is>
       </c>
       <c r="AG72">
+        <v>0</v>
+      </c>
+      <c r="AH72">
+        <v>0</v>
+      </c>
+      <c r="AI72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
         <v>30000</v>
       </c>
-      <c r="AH72">
-        <v>0</v>
-      </c>
-      <c r="AI72">
+      <c r="AM72">
+        <v>0</v>
+      </c>
+      <c r="AN72">
         <v>0</v>
       </c>
     </row>
@@ -8498,12 +9462,27 @@
         <v>2</v>
       </c>
       <c r="AG73">
+        <v>1400</v>
+      </c>
+      <c r="AH73">
+        <v>1000</v>
+      </c>
+      <c r="AI73">
+        <v>2400</v>
+      </c>
+      <c r="AJ73">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="AK73">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="AL73">
         <v>59400</v>
       </c>
-      <c r="AH73">
+      <c r="AM73">
         <v>600</v>
       </c>
-      <c r="AI73">
+      <c r="AN73">
         <v>0</v>
       </c>
     </row>
@@ -8611,12 +9590,27 @@
         <v>3</v>
       </c>
       <c r="AG74">
+        <v>3150</v>
+      </c>
+      <c r="AH74">
+        <v>0</v>
+      </c>
+      <c r="AI74">
+        <v>3150</v>
+      </c>
+      <c r="AJ74">
+        <v>100</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
         <v>60150</v>
       </c>
-      <c r="AH74">
+      <c r="AM74">
         <v>450</v>
       </c>
-      <c r="AI74">
+      <c r="AN74">
         <v>0</v>
       </c>
     </row>
@@ -8724,12 +9718,27 @@
         <v>3</v>
       </c>
       <c r="AG75">
+        <v>3150</v>
+      </c>
+      <c r="AH75">
+        <v>0</v>
+      </c>
+      <c r="AI75">
+        <v>3150</v>
+      </c>
+      <c r="AJ75">
+        <v>100</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
         <v>64150</v>
       </c>
-      <c r="AH75">
+      <c r="AM75">
         <v>-3700</v>
       </c>
-      <c r="AI75">
+      <c r="AN75">
         <v>0</v>
       </c>
     </row>
@@ -8843,12 +9852,27 @@
         <v>4</v>
       </c>
       <c r="AG76">
+        <v>7600</v>
+      </c>
+      <c r="AH76">
+        <v>18000</v>
+      </c>
+      <c r="AI76">
+        <v>25600</v>
+      </c>
+      <c r="AJ76">
+        <v>29.6875</v>
+      </c>
+      <c r="AK76">
+        <v>70.3125</v>
+      </c>
+      <c r="AL76">
         <v>83600</v>
       </c>
-      <c r="AH76">
+      <c r="AM76">
         <v>700</v>
       </c>
-      <c r="AI76">
+      <c r="AN76">
         <v>0</v>
       </c>
     </row>
@@ -8937,12 +9961,21 @@
         </is>
       </c>
       <c r="AG77">
+        <v>0</v>
+      </c>
+      <c r="AH77">
+        <v>0</v>
+      </c>
+      <c r="AI77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
         <v>50000</v>
       </c>
-      <c r="AH77">
+      <c r="AM77">
         <v>15000</v>
       </c>
-      <c r="AI77">
+      <c r="AN77">
         <v>0</v>
       </c>
     </row>
@@ -9047,12 +10080,21 @@
         <v>5</v>
       </c>
       <c r="AG78">
+        <v>0</v>
+      </c>
+      <c r="AH78">
+        <v>0</v>
+      </c>
+      <c r="AI78">
+        <v>0</v>
+      </c>
+      <c r="AL78">
         <v>113000</v>
       </c>
-      <c r="AH78">
+      <c r="AM78">
         <v>-8000</v>
       </c>
-      <c r="AI78">
+      <c r="AN78">
         <v>0</v>
       </c>
     </row>
@@ -9157,12 +10199,21 @@
         <v>5</v>
       </c>
       <c r="AG79">
+        <v>0</v>
+      </c>
+      <c r="AH79">
+        <v>0</v>
+      </c>
+      <c r="AI79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
         <v>87000</v>
       </c>
-      <c r="AH79">
+      <c r="AM79">
         <v>-5000</v>
       </c>
-      <c r="AI79">
+      <c r="AN79">
         <v>0</v>
       </c>
     </row>
@@ -9267,12 +10318,21 @@
         <v>5</v>
       </c>
       <c r="AG80">
+        <v>0</v>
+      </c>
+      <c r="AH80">
+        <v>0</v>
+      </c>
+      <c r="AI80">
+        <v>0</v>
+      </c>
+      <c r="AL80">
         <v>87000</v>
       </c>
-      <c r="AH80">
+      <c r="AM80">
         <v>-2000</v>
       </c>
-      <c r="AI80">
+      <c r="AN80">
         <v>0</v>
       </c>
     </row>
@@ -9386,12 +10446,27 @@
         <v>5</v>
       </c>
       <c r="AG81">
+        <v>10000</v>
+      </c>
+      <c r="AH81">
+        <v>6000</v>
+      </c>
+      <c r="AI81">
+        <v>16000</v>
+      </c>
+      <c r="AJ81">
+        <v>62.5</v>
+      </c>
+      <c r="AK81">
+        <v>37.5</v>
+      </c>
+      <c r="AL81">
         <v>169000</v>
       </c>
-      <c r="AH81">
+      <c r="AM81">
         <v>1000</v>
       </c>
-      <c r="AI81">
+      <c r="AN81">
         <v>0</v>
       </c>
     </row>
@@ -9480,12 +10555,21 @@
         </is>
       </c>
       <c r="AG82">
+        <v>0</v>
+      </c>
+      <c r="AH82">
+        <v>0</v>
+      </c>
+      <c r="AI82">
+        <v>0</v>
+      </c>
+      <c r="AL82">
         <v>75000</v>
       </c>
-      <c r="AH82">
+      <c r="AM82">
         <v>50000</v>
       </c>
-      <c r="AI82">
+      <c r="AN82">
         <v>0</v>
       </c>
     </row>
@@ -9599,12 +10683,27 @@
         <v>4</v>
       </c>
       <c r="AG83">
+        <v>10500</v>
+      </c>
+      <c r="AH83">
+        <v>17000</v>
+      </c>
+      <c r="AI83">
+        <v>27500</v>
+      </c>
+      <c r="AJ83">
+        <v>38.18181818181819</v>
+      </c>
+      <c r="AK83">
+        <v>61.81818181818181</v>
+      </c>
+      <c r="AL83">
         <v>137500</v>
       </c>
-      <c r="AH83">
+      <c r="AM83">
         <v>42500</v>
       </c>
-      <c r="AI83">
+      <c r="AN83">
         <v>0</v>
       </c>
     </row>
@@ -9712,12 +10811,27 @@
         <v>4</v>
       </c>
       <c r="AG84">
+        <v>25500</v>
+      </c>
+      <c r="AH84">
+        <v>0</v>
+      </c>
+      <c r="AI84">
+        <v>25500</v>
+      </c>
+      <c r="AJ84">
+        <v>100</v>
+      </c>
+      <c r="AK84">
+        <v>0</v>
+      </c>
+      <c r="AL84">
         <v>135500</v>
       </c>
-      <c r="AH84">
+      <c r="AM84">
         <v>37000</v>
       </c>
-      <c r="AI84">
+      <c r="AN84">
         <v>0</v>
       </c>
     </row>
@@ -9831,12 +10945,27 @@
         <v>5</v>
       </c>
       <c r="AG85">
+        <v>25500</v>
+      </c>
+      <c r="AH85">
+        <v>16000</v>
+      </c>
+      <c r="AI85">
+        <v>41500</v>
+      </c>
+      <c r="AJ85">
+        <v>61.44578313253012</v>
+      </c>
+      <c r="AK85">
+        <v>38.55421686746988</v>
+      </c>
+      <c r="AL85">
         <v>151500</v>
       </c>
-      <c r="AH85">
+      <c r="AM85">
         <v>15500</v>
       </c>
-      <c r="AI85">
+      <c r="AN85">
         <v>0</v>
       </c>
     </row>
@@ -9944,12 +11073,27 @@
         <v>4</v>
       </c>
       <c r="AG86">
+        <v>25500</v>
+      </c>
+      <c r="AH86">
+        <v>0</v>
+      </c>
+      <c r="AI86">
+        <v>25500</v>
+      </c>
+      <c r="AJ86">
+        <v>100</v>
+      </c>
+      <c r="AK86">
+        <v>0</v>
+      </c>
+      <c r="AL86">
         <v>140500</v>
       </c>
-      <c r="AH86">
+      <c r="AM86">
         <v>5000</v>
       </c>
-      <c r="AI86">
+      <c r="AN86">
         <v>0</v>
       </c>
     </row>
@@ -10038,12 +11182,21 @@
         </is>
       </c>
       <c r="AG87">
+        <v>0</v>
+      </c>
+      <c r="AH87">
+        <v>0</v>
+      </c>
+      <c r="AI87">
+        <v>0</v>
+      </c>
+      <c r="AL87">
         <v>115000</v>
       </c>
-      <c r="AH87">
+      <c r="AM87">
         <v>80000</v>
       </c>
-      <c r="AI87">
+      <c r="AN87">
         <v>0</v>
       </c>
     </row>
@@ -10157,12 +11310,27 @@
         <v>4</v>
       </c>
       <c r="AG88">
+        <v>4000</v>
+      </c>
+      <c r="AH88">
+        <v>23000</v>
+      </c>
+      <c r="AI88">
+        <v>27000</v>
+      </c>
+      <c r="AJ88">
+        <v>14.81481481481481</v>
+      </c>
+      <c r="AK88">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="AL88">
         <v>177000</v>
       </c>
-      <c r="AH88">
+      <c r="AM88">
         <v>93000</v>
       </c>
-      <c r="AI88">
+      <c r="AN88">
         <v>0</v>
       </c>
     </row>
@@ -10276,12 +11444,27 @@
         <v>4</v>
       </c>
       <c r="AG89">
+        <v>19000</v>
+      </c>
+      <c r="AH89">
+        <v>10000</v>
+      </c>
+      <c r="AI89">
+        <v>29000</v>
+      </c>
+      <c r="AJ89">
+        <v>65.51724137931035</v>
+      </c>
+      <c r="AK89">
+        <v>34.48275862068966</v>
+      </c>
+      <c r="AL89">
         <v>179000</v>
       </c>
-      <c r="AH89">
+      <c r="AM89">
         <v>104000</v>
       </c>
-      <c r="AI89">
+      <c r="AN89">
         <v>0</v>
       </c>
     </row>
@@ -10389,12 +11572,27 @@
         <v>4</v>
       </c>
       <c r="AG90">
+        <v>28500</v>
+      </c>
+      <c r="AH90">
+        <v>0</v>
+      </c>
+      <c r="AI90">
+        <v>28500</v>
+      </c>
+      <c r="AJ90">
+        <v>100</v>
+      </c>
+      <c r="AK90">
+        <v>0</v>
+      </c>
+      <c r="AL90">
         <v>178500</v>
       </c>
-      <c r="AH90">
+      <c r="AM90">
         <v>115500</v>
       </c>
-      <c r="AI90">
+      <c r="AN90">
         <v>0</v>
       </c>
     </row>
@@ -10502,12 +11700,27 @@
         <v>4</v>
       </c>
       <c r="AG91">
+        <v>28500</v>
+      </c>
+      <c r="AH91">
+        <v>0</v>
+      </c>
+      <c r="AI91">
+        <v>28500</v>
+      </c>
+      <c r="AJ91">
+        <v>100</v>
+      </c>
+      <c r="AK91">
+        <v>0</v>
+      </c>
+      <c r="AL91">
         <v>183500</v>
       </c>
-      <c r="AH91">
+      <c r="AM91">
         <v>122000</v>
       </c>
-      <c r="AI91">
+      <c r="AN91">
         <v>0</v>
       </c>
     </row>
@@ -10596,12 +11809,21 @@
         </is>
       </c>
       <c r="AG92">
+        <v>0</v>
+      </c>
+      <c r="AH92">
+        <v>0</v>
+      </c>
+      <c r="AI92">
+        <v>0</v>
+      </c>
+      <c r="AL92">
         <v>40000</v>
       </c>
-      <c r="AH92">
+      <c r="AM92">
         <v>5000</v>
       </c>
-      <c r="AI92">
+      <c r="AN92">
         <v>0</v>
       </c>
     </row>
@@ -10706,12 +11928,21 @@
         <v>5</v>
       </c>
       <c r="AG93">
+        <v>0</v>
+      </c>
+      <c r="AH93">
+        <v>0</v>
+      </c>
+      <c r="AI93">
+        <v>0</v>
+      </c>
+      <c r="AL93">
         <v>89000</v>
       </c>
-      <c r="AH93">
+      <c r="AM93">
         <v>-9000</v>
       </c>
-      <c r="AI93">
+      <c r="AN93">
         <v>0</v>
       </c>
     </row>
@@ -10816,12 +12047,21 @@
         <v>5</v>
       </c>
       <c r="AG94">
+        <v>0</v>
+      </c>
+      <c r="AH94">
+        <v>0</v>
+      </c>
+      <c r="AI94">
+        <v>0</v>
+      </c>
+      <c r="AL94">
         <v>70000</v>
       </c>
-      <c r="AH94">
+      <c r="AM94">
         <v>-4000</v>
       </c>
-      <c r="AI94">
+      <c r="AN94">
         <v>0</v>
       </c>
     </row>
@@ -10929,12 +12169,27 @@
         <v>5</v>
       </c>
       <c r="AG95">
+        <v>3125</v>
+      </c>
+      <c r="AH95">
+        <v>0</v>
+      </c>
+      <c r="AI95">
+        <v>3125</v>
+      </c>
+      <c r="AJ95">
+        <v>100</v>
+      </c>
+      <c r="AK95">
+        <v>0</v>
+      </c>
+      <c r="AL95">
         <v>81125</v>
       </c>
-      <c r="AH95">
+      <c r="AM95">
         <v>-10125</v>
       </c>
-      <c r="AI95">
+      <c r="AN95">
         <v>0</v>
       </c>
     </row>
@@ -11039,12 +12294,21 @@
         <v>5</v>
       </c>
       <c r="AG96">
+        <v>0</v>
+      </c>
+      <c r="AH96">
+        <v>0</v>
+      </c>
+      <c r="AI96">
+        <v>0</v>
+      </c>
+      <c r="AL96">
         <v>66000</v>
       </c>
-      <c r="AH96">
+      <c r="AM96">
         <v>-1125</v>
       </c>
-      <c r="AI96">
+      <c r="AN96">
         <v>0</v>
       </c>
     </row>
@@ -11133,12 +12397,21 @@
         </is>
       </c>
       <c r="AG97">
+        <v>0</v>
+      </c>
+      <c r="AH97">
+        <v>0</v>
+      </c>
+      <c r="AI97">
+        <v>0</v>
+      </c>
+      <c r="AL97">
         <v>60000</v>
       </c>
-      <c r="AH97">
+      <c r="AM97">
         <v>30000</v>
       </c>
-      <c r="AI97">
+      <c r="AN97">
         <v>0</v>
       </c>
     </row>
@@ -11246,12 +12519,27 @@
         <v>5</v>
       </c>
       <c r="AG98">
+        <v>0</v>
+      </c>
+      <c r="AH98">
+        <v>14000</v>
+      </c>
+      <c r="AI98">
+        <v>14000</v>
+      </c>
+      <c r="AJ98">
+        <v>0</v>
+      </c>
+      <c r="AK98">
+        <v>100</v>
+      </c>
+      <c r="AL98">
         <v>114000</v>
       </c>
-      <c r="AH98">
+      <c r="AM98">
         <v>26000</v>
       </c>
-      <c r="AI98">
+      <c r="AN98">
         <v>0</v>
       </c>
     </row>
@@ -11365,12 +12653,27 @@
         <v>5</v>
       </c>
       <c r="AG99">
+        <v>16700</v>
+      </c>
+      <c r="AH99">
+        <v>1000</v>
+      </c>
+      <c r="AI99">
+        <v>17700</v>
+      </c>
+      <c r="AJ99">
+        <v>94.35028248587571</v>
+      </c>
+      <c r="AK99">
+        <v>5.649717514124294</v>
+      </c>
+      <c r="AL99">
         <v>113700</v>
       </c>
-      <c r="AH99">
+      <c r="AM99">
         <v>22300</v>
       </c>
-      <c r="AI99">
+      <c r="AN99">
         <v>0</v>
       </c>
     </row>
@@ -11484,12 +12787,27 @@
         <v>2</v>
       </c>
       <c r="AG100">
+        <v>20700</v>
+      </c>
+      <c r="AH100">
+        <v>8000</v>
+      </c>
+      <c r="AI100">
+        <v>28700</v>
+      </c>
+      <c r="AJ100">
+        <v>72.12543554006969</v>
+      </c>
+      <c r="AK100">
+        <v>27.87456445993031</v>
+      </c>
+      <c r="AL100">
         <v>128700</v>
       </c>
-      <c r="AH100">
+      <c r="AM100">
         <v>3600</v>
       </c>
-      <c r="AI100">
+      <c r="AN100">
         <v>0</v>
       </c>
     </row>
@@ -11597,12 +12915,27 @@
         <v>2</v>
       </c>
       <c r="AG101">
+        <v>11200</v>
+      </c>
+      <c r="AH101">
+        <v>0</v>
+      </c>
+      <c r="AI101">
+        <v>11200</v>
+      </c>
+      <c r="AJ101">
+        <v>100</v>
+      </c>
+      <c r="AK101">
+        <v>0</v>
+      </c>
+      <c r="AL101">
         <v>107200</v>
       </c>
-      <c r="AH101">
+      <c r="AM101">
         <v>6400</v>
       </c>
-      <c r="AI101">
+      <c r="AN101">
         <v>0</v>
       </c>
     </row>
@@ -11691,12 +13024,21 @@
         </is>
       </c>
       <c r="AG102">
+        <v>0</v>
+      </c>
+      <c r="AH102">
+        <v>0</v>
+      </c>
+      <c r="AI102">
+        <v>0</v>
+      </c>
+      <c r="AL102">
         <v>30000</v>
       </c>
-      <c r="AH102">
-        <v>0</v>
-      </c>
-      <c r="AI102">
+      <c r="AM102">
+        <v>0</v>
+      </c>
+      <c r="AN102">
         <v>0</v>
       </c>
     </row>
@@ -11810,12 +13152,27 @@
         <v>2</v>
       </c>
       <c r="AG103">
+        <v>1400</v>
+      </c>
+      <c r="AH103">
+        <v>1000</v>
+      </c>
+      <c r="AI103">
+        <v>2400</v>
+      </c>
+      <c r="AJ103">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="AK103">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="AL103">
         <v>58400</v>
       </c>
-      <c r="AH103">
+      <c r="AM103">
         <v>1600</v>
       </c>
-      <c r="AI103">
+      <c r="AN103">
         <v>0</v>
       </c>
     </row>
@@ -11929,12 +13286,27 @@
         <v>2</v>
       </c>
       <c r="AG104">
+        <v>1400</v>
+      </c>
+      <c r="AH104">
+        <v>8000</v>
+      </c>
+      <c r="AI104">
+        <v>9400</v>
+      </c>
+      <c r="AJ104">
+        <v>14.8936170212766</v>
+      </c>
+      <c r="AK104">
+        <v>85.1063829787234</v>
+      </c>
+      <c r="AL104">
         <v>61400</v>
       </c>
-      <c r="AH104">
+      <c r="AM104">
         <v>200</v>
       </c>
-      <c r="AI104">
+      <c r="AN104">
         <v>0</v>
       </c>
     </row>
@@ -12048,12 +13420,27 @@
         <v>2</v>
       </c>
       <c r="AG105">
+        <v>1400</v>
+      </c>
+      <c r="AH105">
+        <v>6000</v>
+      </c>
+      <c r="AI105">
+        <v>7400</v>
+      </c>
+      <c r="AJ105">
+        <v>18.91891891891892</v>
+      </c>
+      <c r="AK105">
+        <v>81.08108108108108</v>
+      </c>
+      <c r="AL105">
         <v>59400</v>
       </c>
-      <c r="AH105">
+      <c r="AM105">
         <v>800</v>
       </c>
-      <c r="AI105">
+      <c r="AN105">
         <v>0</v>
       </c>
     </row>
@@ -12161,12 +13548,27 @@
         <v>1</v>
       </c>
       <c r="AG106">
+        <v>0</v>
+      </c>
+      <c r="AH106">
+        <v>8000</v>
+      </c>
+      <c r="AI106">
+        <v>8000</v>
+      </c>
+      <c r="AJ106">
+        <v>0</v>
+      </c>
+      <c r="AK106">
+        <v>100</v>
+      </c>
+      <c r="AL106">
         <v>60000</v>
       </c>
-      <c r="AH106">
+      <c r="AM106">
         <v>800</v>
       </c>
-      <c r="AI106">
+      <c r="AN106">
         <v>0</v>
       </c>
     </row>
@@ -12255,12 +13657,21 @@
         </is>
       </c>
       <c r="AG107">
+        <v>0</v>
+      </c>
+      <c r="AH107">
+        <v>0</v>
+      </c>
+      <c r="AI107">
+        <v>0</v>
+      </c>
+      <c r="AL107">
         <v>50000</v>
       </c>
-      <c r="AH107">
+      <c r="AM107">
         <v>15000</v>
       </c>
-      <c r="AI107">
+      <c r="AN107">
         <v>0</v>
       </c>
     </row>
@@ -12368,12 +13779,27 @@
         <v>1</v>
       </c>
       <c r="AG108">
+        <v>0</v>
+      </c>
+      <c r="AH108">
+        <v>19000</v>
+      </c>
+      <c r="AI108">
+        <v>19000</v>
+      </c>
+      <c r="AJ108">
+        <v>0</v>
+      </c>
+      <c r="AK108">
+        <v>100</v>
+      </c>
+      <c r="AL108">
         <v>95000</v>
       </c>
-      <c r="AH108">
+      <c r="AM108">
         <v>10000</v>
       </c>
-      <c r="AI108">
+      <c r="AN108">
         <v>0</v>
       </c>
     </row>
@@ -12487,12 +13913,27 @@
         <v>2</v>
       </c>
       <c r="AG109">
+        <v>9750</v>
+      </c>
+      <c r="AH109">
+        <v>14000</v>
+      </c>
+      <c r="AI109">
+        <v>23750</v>
+      </c>
+      <c r="AJ109">
+        <v>41.05263157894737</v>
+      </c>
+      <c r="AK109">
+        <v>58.94736842105262</v>
+      </c>
+      <c r="AL109">
         <v>95750</v>
       </c>
-      <c r="AH109">
+      <c r="AM109">
         <v>4250</v>
       </c>
-      <c r="AI109">
+      <c r="AN109">
         <v>0</v>
       </c>
     </row>
@@ -12600,12 +14041,27 @@
         <v>2</v>
       </c>
       <c r="AG110">
+        <v>11150</v>
+      </c>
+      <c r="AH110">
+        <v>0</v>
+      </c>
+      <c r="AI110">
+        <v>11150</v>
+      </c>
+      <c r="AJ110">
+        <v>100</v>
+      </c>
+      <c r="AK110">
+        <v>0</v>
+      </c>
+      <c r="AL110">
         <v>83150</v>
       </c>
-      <c r="AH110">
+      <c r="AM110">
         <v>11100</v>
       </c>
-      <c r="AI110">
+      <c r="AN110">
         <v>0</v>
       </c>
     </row>
@@ -12713,12 +14169,27 @@
         <v>2</v>
       </c>
       <c r="AG111">
+        <v>11150</v>
+      </c>
+      <c r="AH111">
+        <v>0</v>
+      </c>
+      <c r="AI111">
+        <v>11150</v>
+      </c>
+      <c r="AJ111">
+        <v>100</v>
+      </c>
+      <c r="AK111">
+        <v>0</v>
+      </c>
+      <c r="AL111">
         <v>83150</v>
       </c>
-      <c r="AH111">
+      <c r="AM111">
         <v>17950</v>
       </c>
-      <c r="AI111">
+      <c r="AN111">
         <v>0</v>
       </c>
     </row>
@@ -12807,12 +14278,21 @@
         </is>
       </c>
       <c r="AG112">
+        <v>0</v>
+      </c>
+      <c r="AH112">
+        <v>0</v>
+      </c>
+      <c r="AI112">
+        <v>0</v>
+      </c>
+      <c r="AL112">
         <v>75000</v>
       </c>
-      <c r="AH112">
+      <c r="AM112">
         <v>50000</v>
       </c>
-      <c r="AI112">
+      <c r="AN112">
         <v>0</v>
       </c>
     </row>
@@ -12920,12 +14400,27 @@
         <v>4</v>
       </c>
       <c r="AG113">
+        <v>5000</v>
+      </c>
+      <c r="AH113">
+        <v>0</v>
+      </c>
+      <c r="AI113">
+        <v>5000</v>
+      </c>
+      <c r="AJ113">
+        <v>100</v>
+      </c>
+      <c r="AK113">
+        <v>0</v>
+      </c>
+      <c r="AL113">
         <v>114000</v>
       </c>
-      <c r="AH113">
+      <c r="AM113">
         <v>66000</v>
       </c>
-      <c r="AI113">
+      <c r="AN113">
         <v>0</v>
       </c>
     </row>
@@ -13039,12 +14534,27 @@
         <v>4</v>
       </c>
       <c r="AG114">
+        <v>7500</v>
+      </c>
+      <c r="AH114">
+        <v>18000</v>
+      </c>
+      <c r="AI114">
+        <v>25500</v>
+      </c>
+      <c r="AJ114">
+        <v>29.41176470588236</v>
+      </c>
+      <c r="AK114">
+        <v>70.58823529411765</v>
+      </c>
+      <c r="AL114">
         <v>130500</v>
       </c>
-      <c r="AH114">
+      <c r="AM114">
         <v>65500</v>
       </c>
-      <c r="AI114">
+      <c r="AN114">
         <v>0</v>
       </c>
     </row>
@@ -13158,12 +14668,27 @@
         <v>4</v>
       </c>
       <c r="AG115">
+        <v>16000</v>
+      </c>
+      <c r="AH115">
+        <v>15000</v>
+      </c>
+      <c r="AI115">
+        <v>31000</v>
+      </c>
+      <c r="AJ115">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="AK115">
+        <v>48.38709677419355</v>
+      </c>
+      <c r="AL115">
         <v>136000</v>
       </c>
-      <c r="AH115">
+      <c r="AM115">
         <v>59500</v>
       </c>
-      <c r="AI115">
+      <c r="AN115">
         <v>0</v>
       </c>
     </row>
@@ -13271,12 +14796,27 @@
         <v>4</v>
       </c>
       <c r="AG116">
+        <v>16000</v>
+      </c>
+      <c r="AH116">
+        <v>0</v>
+      </c>
+      <c r="AI116">
+        <v>16000</v>
+      </c>
+      <c r="AJ116">
+        <v>100</v>
+      </c>
+      <c r="AK116">
+        <v>0</v>
+      </c>
+      <c r="AL116">
         <v>126000</v>
       </c>
-      <c r="AH116">
+      <c r="AM116">
         <v>63500</v>
       </c>
-      <c r="AI116">
+      <c r="AN116">
         <v>0</v>
       </c>
     </row>
@@ -13365,12 +14905,21 @@
         </is>
       </c>
       <c r="AG117">
+        <v>0</v>
+      </c>
+      <c r="AH117">
+        <v>0</v>
+      </c>
+      <c r="AI117">
+        <v>0</v>
+      </c>
+      <c r="AL117">
         <v>115000</v>
       </c>
-      <c r="AH117">
+      <c r="AM117">
         <v>80000</v>
       </c>
-      <c r="AI117">
+      <c r="AN117">
         <v>0</v>
       </c>
     </row>
@@ -13484,12 +15033,27 @@
         <v>4</v>
       </c>
       <c r="AG118">
+        <v>3200</v>
+      </c>
+      <c r="AH118">
+        <v>14000</v>
+      </c>
+      <c r="AI118">
+        <v>17200</v>
+      </c>
+      <c r="AJ118">
+        <v>18.6046511627907</v>
+      </c>
+      <c r="AK118">
+        <v>81.3953488372093</v>
+      </c>
+      <c r="AL118">
         <v>172200</v>
       </c>
-      <c r="AH118">
+      <c r="AM118">
         <v>97800</v>
       </c>
-      <c r="AI118">
+      <c r="AN118">
         <v>0</v>
       </c>
     </row>
@@ -13597,12 +15161,27 @@
         <v>4</v>
       </c>
       <c r="AG119">
+        <v>24700</v>
+      </c>
+      <c r="AH119">
+        <v>0</v>
+      </c>
+      <c r="AI119">
+        <v>24700</v>
+      </c>
+      <c r="AJ119">
+        <v>100</v>
+      </c>
+      <c r="AK119">
+        <v>0</v>
+      </c>
+      <c r="AL119">
         <v>175700</v>
       </c>
-      <c r="AH119">
+      <c r="AM119">
         <v>112100</v>
       </c>
-      <c r="AI119">
+      <c r="AN119">
         <v>0</v>
       </c>
     </row>
@@ -13716,12 +15295,27 @@
         <v>4</v>
       </c>
       <c r="AG120">
+        <v>11200</v>
+      </c>
+      <c r="AH120">
+        <v>10000</v>
+      </c>
+      <c r="AI120">
+        <v>21200</v>
+      </c>
+      <c r="AJ120">
+        <v>52.83018867924528</v>
+      </c>
+      <c r="AK120">
+        <v>47.16981132075472</v>
+      </c>
+      <c r="AL120">
         <v>176200</v>
       </c>
-      <c r="AH120">
+      <c r="AM120">
         <v>125900</v>
       </c>
-      <c r="AI120">
+      <c r="AN120">
         <v>0</v>
       </c>
     </row>
@@ -13835,12 +15429,27 @@
         <v>4</v>
       </c>
       <c r="AG121">
+        <v>24700</v>
+      </c>
+      <c r="AH121">
+        <v>8000</v>
+      </c>
+      <c r="AI121">
+        <v>32700</v>
+      </c>
+      <c r="AJ121">
+        <v>75.53516819571865</v>
+      </c>
+      <c r="AK121">
+        <v>24.46483180428135</v>
+      </c>
+      <c r="AL121">
         <v>183700</v>
       </c>
-      <c r="AH121">
+      <c r="AM121">
         <v>132200</v>
       </c>
-      <c r="AI121">
+      <c r="AN121">
         <v>0</v>
       </c>
     </row>
